--- a/management/product backlog template.xlsx
+++ b/management/product backlog template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65E3B90D-658D-1D4D-95E4-853C40A4EE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B06739F-66FC-4F7B-8ACC-517FFB405F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Story ID</t>
   </si>
@@ -60,24 +60,79 @@
   <si>
     <t>Date finished (or planned)</t>
   </si>
+  <si>
+    <t>US-D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data Storage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a Developer, I want to implement a File I/O handler, so that all recruitment data is saved in .txt/csv files without using a database.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strictly follow the project's restriction that prohibits the use of the database.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a Developer, I want to create a central authentication check, so that TA, MO and admin can only get access to their own functions (like only MO can delete jobs).</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>US-D02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Role Permission Control</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Protect system security, ensure stable functions and safeguard personal privacy.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>US-T01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main Workflow Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a Tester, I want to execute an end-to-end test from registration to job application, so that I can ensure the main workflow don't have any bug.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The key step in verifying the stability of the system.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -136,8 +191,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - 着色 1" xfId="1" builtinId="31"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -439,21 +494,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1"/>
+    <col min="4" max="4" width="9.1328125" style="1"/>
     <col min="5" max="5" width="28.33203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="19.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="19.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.796875" style="1" customWidth="1"/>
     <col min="10" max="10" width="26.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -485,7 +540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="112" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="94.5" x14ac:dyDescent="0.3">
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
@@ -493,7 +548,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="3" spans="1:10" ht="81" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="81" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/management/product backlog template.xlsx
+++ b/management/product backlog template.xlsx
@@ -1,96 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65E3B90D-658D-1D4D-95E4-853C40A4EE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Story ID</t>
-  </si>
-  <si>
-    <t>Story Name</t>
-  </si>
-  <si>
-    <t>Acceptance Criteria</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Iteration (Sprint) number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is an example.
-This is a new line
-1. List 1
-2. List 2
-3. List 3
-</t>
-  </si>
-  <si>
-    <t>Estimation</t>
-  </si>
-  <si>
-    <t>This is an example.
-As a &lt;&gt;
-I want &lt;&gt;
-So that &lt;&gt;</t>
-  </si>
-  <si>
-    <t>Date started (or planned)</t>
-  </si>
-  <si>
-    <t>Date finished (or planned)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="宋体"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -120,35 +78,94 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - 着色 1" xfId="1" builtinId="31"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -438,63 +455,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1"/>
-    <col min="5" max="5" width="28.33203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="19.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.33203125" style="1" customWidth="1"/>
+    <col width="9.1328125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16.6640625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="36" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.1328125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="28.33203125" customWidth="1" style="1" min="5" max="5"/>
+    <col width="19.796875" customWidth="1" style="1" min="6" max="7"/>
+    <col width="17.1328125" customWidth="1" style="1" min="8" max="8"/>
+    <col width="24.796875" customWidth="1" style="1" min="9" max="9"/>
+    <col width="26.33203125" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="112" x14ac:dyDescent="0.2">
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Story ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Story Name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Iteration (Sprint) number</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Estimation</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Date started (or planned)</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Date finished (or planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="94.5" customHeight="1">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>This is an example.
+As a &lt;&gt;
+I want &lt;&gt;
+So that &lt;&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is an example.
+This is a new line
+1. List 1
+2. List 2
+3. List 3
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>US-D01</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Data Storage</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>As a Developer, I want to implement a File I/O handler, so that all recruitment data is saved in .txt/csv files without using a database.</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Strictly follow the project's restriction that prohibits the use of the database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>US-D02</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Role Permission Control</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>As a Developer, I want to create a central authentication check, so that TA, MO and admin can only get access to their own functions (like only MO can delete jobs).</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Protect system security, ensure stable functions and safeguard personal privacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="67.5" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>US-T01</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Main Workflow Test</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>As a Tester, I want to execute an end-to-end test from registration to job application, so that I can ensure the main workflow don't have any bug.</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>The key step in verifying the stability of the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TA-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Create profile</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The applicant can create a personal profile in the system and fill in basic information such as student ID, programme, year of study and contact details.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Basic personal information for later applications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TA-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Upload CV</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The applicant can upload a CV to support future job applications. The file should be easy to update if needed.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CV upload before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TA-03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>View available jobs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The applicant can view current TA vacancies in the system, including key information such as module name, requirements and deadline.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Job list with basic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TA-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apply for a job</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The applicant can submit an application for a TA position through the system using the information already provided in the profile and CV.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Link application with profile and CV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TA-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Check application status</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The applicant can check the progress of submitted applications, for example whether an application has been received, is under review, or has a final result.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Status tracking page.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
--- a/management/product backlog template.xlsx
+++ b/management/product backlog template.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65E3B90D-658D-1D4D-95E4-853C40A4EE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="11520" windowHeight="9780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>Story ID</t>
   </si>
@@ -23,19 +35,34 @@
     <t>Story Name</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Iteration (Sprint) number</t>
+  </si>
+  <si>
     <t>Acceptance Criteria</t>
   </si>
   <si>
-    <t>Priority</t>
+    <t>Estimation</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Iteration (Sprint) number</t>
+    <t>Date started (or planned)</t>
+  </si>
+  <si>
+    <t>Date finished (or planned)</t>
+  </si>
+  <si>
+    <t>This is an example.
+As a &lt;&gt;
+I want &lt;&gt;
+So that &lt;&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">This is an example.
@@ -46,42 +73,297 @@
 </t>
   </si>
   <si>
-    <t>Estimation</t>
-  </si>
-  <si>
-    <t>This is an example.
-As a &lt;&gt;
-I want &lt;&gt;
-So that &lt;&gt;</t>
-  </si>
-  <si>
-    <t>Date started (or planned)</t>
-  </si>
-  <si>
-    <t>Date finished (or planned)</t>
+    <t>US-D01</t>
+  </si>
+  <si>
+    <t>Data Storage</t>
+  </si>
+  <si>
+    <t>As a Developer, I want to implement a File I/O handler, so that all recruitment data is saved in .txt/csv files without using a database.</t>
+  </si>
+  <si>
+    <t>Must</t>
+  </si>
+  <si>
+    <t>Strictly follow the project's restriction that prohibits the use of the database.</t>
+  </si>
+  <si>
+    <t>US-D02</t>
+  </si>
+  <si>
+    <t>Role Permission Control</t>
+  </si>
+  <si>
+    <t>As a Developer, I want to create a central authentication check, so that TA, MO and admin can only get access to their own functions (like only MO can delete jobs).</t>
+  </si>
+  <si>
+    <t>Protect system security, ensure stable functions and safeguard personal privacy.</t>
+  </si>
+  <si>
+    <t>US-T01</t>
+  </si>
+  <si>
+    <t>Main Workflow Test</t>
+  </si>
+  <si>
+    <t>As a Tester, I want to execute an end-to-end test from registration to job application, so that I can ensure the main workflow don't have any bug.</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>The key step in verifying the stability of the system.</t>
+  </si>
+  <si>
+    <t>US-C01</t>
+  </si>
+  <si>
+    <t>Overall Recruitment Monitoring</t>
+  </si>
+  <si>
+    <t>As a school administrator,
+I hope to monitor the recruitment progress of all subject modules on a dashboard, so that I can keep track of the vacancies in teaching positions.</t>
+  </si>
+  <si>
+    <t>From a global management perspective, solve the problem of statistical opacity.</t>
+  </si>
+  <si>
+    <t>US-C02</t>
+  </si>
+  <si>
+    <t>Application History Archive</t>
+  </si>
+  <si>
+    <t>As an HR professional, I would like to store and retrieve the past TA application data and feedback information in a simple text format, and also be able to preserve the records for a long time.</t>
+  </si>
+  <si>
+    <t>Comply with the restrictions of "no use of database" and "data interoperability"</t>
+  </si>
+  <si>
+    <t>TA-01</t>
+  </si>
+  <si>
+    <t>Create profile</t>
+  </si>
+  <si>
+    <t>The applicant can create a personal profile in the system and fill in basic information such as student ID, programme, year of study and contact details.</t>
+  </si>
+  <si>
+    <t>Basic personal information for later applications.</t>
+  </si>
+  <si>
+    <t>TA-02</t>
+  </si>
+  <si>
+    <t>Upload CV</t>
+  </si>
+  <si>
+    <t>The applicant can upload a CV to support future job applications. The file should be easy to update if needed.</t>
+  </si>
+  <si>
+    <t>CV upload before applying.</t>
+  </si>
+  <si>
+    <t>TA-03</t>
+  </si>
+  <si>
+    <t>View available jobs</t>
+  </si>
+  <si>
+    <t>The applicant can view current TA vacancies in the system, including key information such as module name, requirements and deadline.</t>
+  </si>
+  <si>
+    <t>Job list with basic information.</t>
+  </si>
+  <si>
+    <t>TA-04</t>
+  </si>
+  <si>
+    <t>Apply for a job</t>
+  </si>
+  <si>
+    <t>The applicant can submit an application for a TA position through the system using the information already provided in the profile and CV.</t>
+  </si>
+  <si>
+    <t>Link application with profile and CV.</t>
+  </si>
+  <si>
+    <t>TA-05</t>
+  </si>
+  <si>
+    <t>Check application status</t>
+  </si>
+  <si>
+    <t>The applicant can check the progress of submitted applications, for example whether an application has been received, is under review, or has a final result.</t>
+  </si>
+  <si>
+    <t>Status tracking page.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -90,12 +372,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -105,48 +567,330 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="27" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -433,68 +1177,239 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="8.7962962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.12962962962963" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1"/>
-    <col min="5" max="5" width="28.33203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="19.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.12962962962963" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="7" width="19.7962962962963" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1296296296296" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7962962962963" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" ht="27" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="94.5" customHeight="1" spans="1:10">
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1">
+        <v>5</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="67.5" customHeight="1" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="100.8" spans="1:10">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="1">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1" spans="1:10">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>11</v>
+      <c r="H7" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="112" x14ac:dyDescent="0.2">
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/management/product backlog template.xlsx
+++ b/management/product backlog template.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65E3B90D-658D-1D4D-95E4-853C40A4EE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>Story ID</t>
   </si>
@@ -23,19 +24,34 @@
     <t>Story Name</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Iteration (Sprint) number</t>
+  </si>
+  <si>
     <t>Acceptance Criteria</t>
   </si>
   <si>
-    <t>Priority</t>
+    <t>Estimation</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Iteration (Sprint) number</t>
+    <t>Date started (or planned)</t>
+  </si>
+  <si>
+    <t>Date finished (or planned)</t>
+  </si>
+  <si>
+    <t>This is an example.
+As a &lt;&gt;
+I want &lt;&gt;
+So that &lt;&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">This is an example.
@@ -46,42 +62,234 @@
 </t>
   </si>
   <si>
-    <t>Estimation</t>
-  </si>
-  <si>
-    <t>This is an example.
-As a &lt;&gt;
-I want &lt;&gt;
-So that &lt;&gt;</t>
-  </si>
-  <si>
-    <t>Date started (or planned)</t>
-  </si>
-  <si>
-    <t>Date finished (or planned)</t>
+    <t>US-D01</t>
+  </si>
+  <si>
+    <t>Data Storage</t>
+  </si>
+  <si>
+    <t>As a Developer, I want to implement a File I/O handler, so that all recruitment data is saved in .txt/csv files without using a database.</t>
+  </si>
+  <si>
+    <t>Strictly follow the project's restriction that prohibits the use of the database.</t>
+  </si>
+  <si>
+    <t>US-D02</t>
+  </si>
+  <si>
+    <t>Role Permission Control</t>
+  </si>
+  <si>
+    <t>As a Developer, I want to create a central authentication check, so that TA, MO and admin can only get access to their own functions (like only MO can delete jobs).</t>
+  </si>
+  <si>
+    <t>Protect system security, ensure stable functions and safeguard personal privacy.</t>
+  </si>
+  <si>
+    <t>US-T01</t>
+  </si>
+  <si>
+    <t>Main Workflow Test</t>
+  </si>
+  <si>
+    <t>As a Tester, I want to execute an end-to-end test from registration to job application, so that I can ensure the main workflow don't have any bug.</t>
+  </si>
+  <si>
+    <t>The key step in verifying the stability of the system.</t>
+  </si>
+  <si>
+    <t>ADM-001</t>
+  </si>
+  <si>
+    <t>View Overall TA Workload</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to check the overall workload of all Teaching Assistants across different modules and activities, so that I can ensure a fair distribution of tasks and prevent overloading.</t>
+  </si>
+  <si>
+    <t>Core Requirement. The system must aggregate data from assigned jobs. Read/write operations must use simple text files (e.g., CSV, JSON), strictly adhering to the "no database" rule.</t>
+  </si>
+  <si>
+    <t>ADM-002</t>
+  </si>
+  <si>
+    <t>AI-Assisted Workload Balancing</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to receive AI-generated recommendations for balancing the workload among TAs, so that I can efficiently reassign tasks if someone is overbooked or underutilized.</t>
+  </si>
+  <si>
+    <t>AI Feature. AI outputs must not be blindly accepted; the system must provide explainable results and structured logic for its recommendations.</t>
+  </si>
+  <si>
+    <t>ADM-003</t>
+  </si>
+  <si>
+    <t>Monitor Global Recruitment Status</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to view a dashboard summarizing the global recruitment status (total jobs posted, applications pending, positions filled), so that I can track the overall progress of the TA recruitment for the semester.</t>
+  </si>
+  <si>
+    <t>Helps streamline the workflow from the previous Excel/forms process. Requires parsing and summarizing data from the plain text storage system.</t>
+  </si>
+  <si>
+    <t>ADM-004</t>
+  </si>
+  <si>
+    <t>Manage User Accounts</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to oversee and verify the registered accounts of Module Organisers and Teaching Assistants, so that I can maintain system security and ensure only authorized personnel use the application.</t>
+  </si>
+  <si>
+    <t>Essential for a complete prototype. Account statuses and roles must be managed and persisted within text files (e.g., XML or JSON).</t>
+  </si>
+  <si>
+    <t>ADM-005</t>
+  </si>
+  <si>
+    <t>Export Final Allocation Reports</t>
+  </si>
+  <si>
+    <t>As an Administrator, I want to export the finalized TA allocation and workload data into a standardized format, so that it can be shared with the school's HR or finance departments for payroll and record-keeping.</t>
+  </si>
+  <si>
+    <t>Ensures the system remains compatible with existing data and legacy systems. Output must be in a simple text format like CSV.</t>
+  </si>
+  <si>
+    <t>US-A01</t>
+  </si>
+  <si>
+    <t>US-A02</t>
+  </si>
+  <si>
+    <t>US-A03</t>
+  </si>
+  <si>
+    <t>US-A04</t>
+  </si>
+  <si>
+    <t>US-A05</t>
+  </si>
+  <si>
+    <t>US-C01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C02
+</t>
+  </si>
+  <si>
+    <t>Overall Recruitment Monitoring</t>
+  </si>
+  <si>
+    <t>Application History Archive</t>
+  </si>
+  <si>
+    <t>As a school administrator,
+I hope to monitor the recruitment progress of all subject modules on a dashboard, so that I can keep track of the vacancies in teaching positions.</t>
+  </si>
+  <si>
+    <t>As an HR professional, I would like to store and retrieve the past TA application data and feedback information in a simple text format, and also be able to preserve the records for a long time.</t>
+  </si>
+  <si>
+    <t>Must</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>From a global management perspective, solve the problem of statistical opacity.</t>
+  </si>
+  <si>
+    <t>Comply with the restrictions of "no use of database" and "data interoperability"</t>
+  </si>
+  <si>
+    <t>US-T02</t>
+  </si>
+  <si>
+    <t>Concurrent File Writing Handle</t>
+  </si>
+  <si>
+    <t>As a Developer, I want to implement a file lock or queue mechanism, so that when multiple TAs apply for jobs at the exact same time, the local .txt/.csv data files are not corrupted or overwritten.</t>
+  </si>
+  <si>
+    <t>Important for system stability since we can't use a standard database.</t>
+  </si>
+  <si>
+    <t>US-T03</t>
+  </si>
+  <si>
+    <t>Invalid CV Upload Handle</t>
+  </si>
+  <si>
+    <t>As a Tester, I want to verify the system correctly blocks unsupported file types or oversized files when a TA uploads a CV, so that the application doesn't crash or store malicious files.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Addresses the edge case of user input error to safeguard personal privacy and system security. </t>
+  </si>
+  <si>
+    <t>1. Uploading executable files (e.g., .exe, .sh) or files larger than 10MB must be rejected.
+2. 2. A clear error message (e.g., "Invalid file format. Supported formats: PDF, DOC, DOCX, JPG, PNG") should be displayed on the UI.
+3. Only standard document formats (.pdf, .docx) are saved to the local directory.</t>
+  </si>
+  <si>
+    <t>1. Simulate multiple users submitting data simultaneously. 
+2. The system accurately appends all records into the file without data loss. 
+3. The system does not crash or throw unhandled I/O exceptions during concurrent access.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="300" formatCode="General"/>
+  </numFmts>
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -89,13 +297,17 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill/>
+    <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.599994"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -118,37 +330,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="3" fillId="0" borderId="3" xfId="0"/>
+    <xf numFmtId="300" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="300" fontId="3" fillId="4" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="3" fillId="0" borderId="3" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf fontId="7" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -438,63 +687,311 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
+  <dimension ref="J14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1"/>
-    <col min="5" max="5" width="28.33203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="19.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.16406" style="16" customWidth="1"/>
+    <col min="2" max="2" width="16.6641" style="16" customWidth="1"/>
+    <col min="3" max="3" width="36" style="16" customWidth="1"/>
+    <col min="4" max="4" width="9.16406" style="16"/>
+    <col min="5" max="5" width="28.332" style="16" customWidth="1"/>
+    <col min="6" max="7" width="19.832" style="16" customWidth="1"/>
+    <col min="8" max="8" width="30.0508" style="16" customWidth="1"/>
+    <col min="9" max="9" width="24.832" style="16" customWidth="1"/>
+    <col min="10" max="10" width="26.332" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:10" ht="16">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="3:6" ht="112">
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="10">
+        <v>5</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="7" t="s"/>
+      <c r="G4" s="10">
+        <v>8</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="10">
+        <v>5</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="89.25" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="10" t="s"/>
+      <c r="E6" s="10" t="s"/>
+      <c r="F6" s="10" t="s"/>
+      <c r="G6" s="10" t="s"/>
+      <c r="H6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="11" t="s"/>
+      <c r="J6" s="11" t="s"/>
+    </row>
+    <row r="7" spans="1:10" ht="87" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="10" t="s"/>
+      <c r="E7" s="10" t="s"/>
+      <c r="F7" s="10" t="s"/>
+      <c r="G7" s="10" t="s"/>
+      <c r="H7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="11" t="s"/>
+      <c r="J7" s="11" t="s"/>
+    </row>
+    <row r="8" spans="1:10" ht="88.5" customHeight="1">
+      <c r="A8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="10" t="s"/>
+      <c r="E8" s="10" t="s"/>
+      <c r="F8" s="10" t="s"/>
+      <c r="G8" s="10" t="s"/>
+      <c r="H8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="11" t="s"/>
+      <c r="J8" s="11" t="s"/>
+    </row>
+    <row r="9" spans="1:10" ht="87.75" customHeight="1">
+      <c r="A9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="10" t="s"/>
+      <c r="E9" s="10" t="s"/>
+      <c r="F9" s="10" t="s"/>
+      <c r="G9" s="10" t="s"/>
+      <c r="H9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="11" t="s"/>
+      <c r="J9" s="11" t="s"/>
+    </row>
+    <row r="10" spans="1:10" ht="88.5" customHeight="1">
+      <c r="A10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="10" t="s"/>
+      <c r="E10" s="10" t="s"/>
+      <c r="F10" s="10" t="s"/>
+      <c r="G10" s="10" t="s"/>
+      <c r="H10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="11" t="s"/>
+      <c r="J10" s="11" t="s"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="10">
+        <v>8</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="10">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H12" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="10">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="112" x14ac:dyDescent="0.2">
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
+      <c r="H13" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="10">
+        <v>3</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>